--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EFC7CB7-56C1-4A4B-9D9A-CC4E553B5047}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFA80C07-F074-431B-890F-4896DB7FA408}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7295C3F-A6E0-4D47-A994-0F7ABC57D01D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C814537-DB37-4E05-9046-D24367C026AE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB06F36C-B59C-48E9-9E5D-BB1FAB5AB634}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DF7A89A-02C3-4CA1-83BF-58035FEEF645}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFA80C07-F074-431B-890F-4896DB7FA408}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{742ABA97-0C2E-42FF-A741-C72819B7FC05}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C814537-DB37-4E05-9046-D24367C026AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE26EED3-44FB-49BF-8739-3DDF4C717D6B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DF7A89A-02C3-4CA1-83BF-58035FEEF645}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F1878DD-5486-4774-A7C8-6D327B12EF33}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{742ABA97-0C2E-42FF-A741-C72819B7FC05}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEAA29C4-D6E9-4BCD-BD3A-5E2DA64F5883}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE26EED3-44FB-49BF-8739-3DDF4C717D6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37980444-3C02-4B33-9010-F680AEEF1DA8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F1878DD-5486-4774-A7C8-6D327B12EF33}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{938C4B13-B618-4163-A43C-83F4B0CEA34C}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEAA29C4-D6E9-4BCD-BD3A-5E2DA64F5883}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2E7700D-83C7-4BDE-8B85-96E8CCCFF322}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37980444-3C02-4B33-9010-F680AEEF1DA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A410ACC8-8DBF-4011-946B-C6FCA3B1DD23}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{938C4B13-B618-4163-A43C-83F4B0CEA34C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EA7B8FF-ECD6-4053-8593-786B7C46701D}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -11,6 +11,242 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="77">
+  <si>
+    <t>species_sci</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Dexterity</t>
+  </si>
+  <si>
+    <t>Orycteropus afer</t>
+  </si>
+  <si>
+    <t>Myrmecophaga jubata</t>
+  </si>
+  <si>
+    <t>Dasypus novemcinctus</t>
+  </si>
+  <si>
+    <t>Desmodus rufus</t>
+  </si>
+  <si>
+    <t>Horpyiocepalus leucogostra</t>
+  </si>
+  <si>
+    <t>Myotis</t>
+  </si>
+  <si>
+    <t>Pteropus edulis</t>
+  </si>
+  <si>
+    <t>Rhinolophus</t>
+  </si>
+  <si>
+    <t>Tadarida cynocephala</t>
+  </si>
+  <si>
+    <t>Castor canadensis</t>
+  </si>
+  <si>
+    <t>Otolemur garnettii</t>
+  </si>
+  <si>
+    <t>Galago crassicaudatus</t>
+  </si>
+  <si>
+    <t>Galago senegalensis</t>
+  </si>
+  <si>
+    <t>Camelus</t>
+  </si>
+  <si>
+    <t>Felis catus</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Tamias striatus</t>
+  </si>
+  <si>
+    <t>Myocastor coypus</t>
+  </si>
+  <si>
+    <t>Canis latrans</t>
+  </si>
+  <si>
+    <t>Canis familiaris</t>
+  </si>
+  <si>
+    <t>Elephas maximus</t>
+  </si>
+  <si>
+    <t>Mustela putorius furo</t>
+  </si>
+  <si>
+    <t>Putorius furo</t>
+  </si>
+  <si>
+    <t>Hylobates lar</t>
+  </si>
+  <si>
+    <t>Hylobates syndactylus</t>
+  </si>
+  <si>
+    <t>Capra hircus</t>
+  </si>
+  <si>
+    <t>Spermophilus tridecemlineatus</t>
+  </si>
+  <si>
+    <t>Cavia aperea</t>
+  </si>
+  <si>
+    <t>Cricetus auratus</t>
+  </si>
+  <si>
+    <t>Erinaceus</t>
+  </si>
+  <si>
+    <t>Paraechinus</t>
+  </si>
+  <si>
+    <t>Sus scrofa</t>
+  </si>
+  <si>
+    <t>Equus caballus</t>
+  </si>
+  <si>
+    <t>Potos flavus</t>
+  </si>
+  <si>
+    <t>Lemur catta</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Scalopus aquaticus</t>
+  </si>
+  <si>
+    <t>Ateles ater</t>
+  </si>
+  <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
+    <t>Cebus apella</t>
+  </si>
+  <si>
+    <t>Chlorocebus sabaeus</t>
+  </si>
+  <si>
+    <t>Cercopithecus pygerythrus</t>
+  </si>
+  <si>
+    <t>Lagothrix lagotricha</t>
+  </si>
+  <si>
+    <t>Macaca irus</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Papio papio</t>
+  </si>
+  <si>
+    <t>Saguinus oedipus</t>
+  </si>
+  <si>
+    <t>Saimiri boliviensis boliviensis</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Mus musculus</t>
+  </si>
+  <si>
+    <t>Equus</t>
+  </si>
+  <si>
+    <t>Didelphis virginiana</t>
+  </si>
+  <si>
+    <t>Pongo pygmaeus</t>
+  </si>
+  <si>
+    <t>Manis pentadactyla</t>
+  </si>
+  <si>
+    <t>Trichosurus vulpecula</t>
+  </si>
+  <si>
+    <t>Microsorex hoyi</t>
+  </si>
+  <si>
+    <t>Setonix brachyurus</t>
+  </si>
+  <si>
+    <t>Oryctolagus cuniculus</t>
+  </si>
+  <si>
+    <t>Procyon lotor</t>
+  </si>
+  <si>
+    <t>Rattus norvegicus</t>
+  </si>
+  <si>
+    <t>Procavia capensis</t>
+  </si>
+  <si>
+    <t>Callorhinus ursinus</t>
+  </si>
+  <si>
+    <t>Ovis aries</t>
+  </si>
+  <si>
+    <t>Nycticebus coucang</t>
+  </si>
+  <si>
+    <t>Tachyglossus aculeatus</t>
+  </si>
+  <si>
+    <t>Sciurus hudsonius</t>
+  </si>
+  <si>
+    <t>Tapirus</t>
+  </si>
+  <si>
+    <t>Tarsius</t>
+  </si>
+  <si>
+    <t>Potorous apicalis</t>
+  </si>
+  <si>
+    <t>Tupaia belangeri</t>
+  </si>
+  <si>
+    <t>Tupaia glis</t>
+  </si>
+  <si>
+    <t>Phocoena phocoena</t>
+  </si>
+  <si>
+    <t>Marmota monax</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,773 +590,603 @@
   <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>species_sci</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Dexterity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Orycteropus afer</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Myrmecophaga jubata</t>
-        </is>
+    <row r="3" spans="1:3">
+      <c r="B3" t="s">
+        <v>4</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dasypus novemcinctus</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Dasypus novemcinctus</t>
-        </is>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Desmodus rufus</t>
-        </is>
+    <row r="5" spans="1:3">
+      <c r="B5" t="s">
+        <v>6</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Horpyiocepalus leucogostra</t>
-        </is>
+    <row r="6" spans="1:3">
+      <c r="B6" t="s">
+        <v>7</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Myotis</t>
-        </is>
+    <row r="7" spans="1:3">
+      <c r="B7" t="s">
+        <v>8</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Pteropus edulis</t>
-        </is>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>9</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Rhinolophus</t>
-        </is>
+    <row r="9" spans="1:3">
+      <c r="B9" t="s">
+        <v>10</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Tadarida cynocephala</t>
-        </is>
+    <row r="10" spans="1:3">
+      <c r="B10" t="s">
+        <v>11</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3">
       <c r="C11">
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Castor canadensis</t>
-        </is>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>12</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Otolemur garnettii</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Galago crassicaudatus</t>
-        </is>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
       </c>
       <c r="C13">
         <v>5</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Galago senegalensis</t>
-        </is>
+    <row r="14" spans="1:3">
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
         <v>5</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Camelus</t>
-        </is>
+    <row r="15" spans="1:3">
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Felis catus</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Felis catus</t>
-        </is>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tamias striatus</t>
-        </is>
+    <row r="18" spans="1:3">
+      <c r="B18" t="s">
+        <v>19</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3">
       <c r="C19">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Myocastor coypus</t>
-        </is>
+    <row r="20" spans="1:3">
+      <c r="B20" t="s">
+        <v>20</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3">
       <c r="C21">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Canis latrans</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Canis familiaris</t>
-        </is>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Elephas maximus</t>
-        </is>
+    <row r="23" spans="1:3">
+      <c r="B23" t="s">
+        <v>23</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Mustela putorius furo</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Putorius furo</t>
-        </is>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
+    <row r="25" spans="1:3">
+      <c r="B25" t="s">
+        <v>26</v>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Hylobates syndactylus</t>
-        </is>
+    <row r="26" spans="1:3">
+      <c r="B26" t="s">
+        <v>27</v>
       </c>
       <c r="C26">
         <v>6</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Capra hircus</t>
-        </is>
+    <row r="27" spans="1:3">
+      <c r="B27" t="s">
+        <v>28</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Spermophilus tridecemlineatus</t>
-        </is>
+    <row r="28" spans="1:3">
+      <c r="B28" t="s">
+        <v>29</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Cavia aperea</t>
-        </is>
+    <row r="29" spans="1:3">
+      <c r="B29" t="s">
+        <v>30</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Cricetus auratus</t>
-        </is>
+    <row r="30" spans="1:3">
+      <c r="B30" t="s">
+        <v>31</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Erinaceus</t>
-        </is>
+    <row r="31" spans="1:3">
+      <c r="B31" t="s">
+        <v>32</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Paraechinus</t>
-        </is>
+    <row r="32" spans="1:3">
+      <c r="B32" t="s">
+        <v>33</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Sus scrofa</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Sus scrofa</t>
-        </is>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Equus caballus</t>
-        </is>
+    <row r="34" spans="1:3">
+      <c r="B34" t="s">
+        <v>35</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Potos flavus</t>
-        </is>
+    <row r="35" spans="1:3">
+      <c r="B35" t="s">
+        <v>36</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Lemur catta</t>
-        </is>
+    <row r="36" spans="1:3">
+      <c r="B36" t="s">
+        <v>37</v>
       </c>
       <c r="C36">
         <v>5</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
       </c>
       <c r="C37">
         <v>7</v>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Scalopus aquaticus</t>
-        </is>
+    <row r="38" spans="1:3">
+      <c r="B38" t="s">
+        <v>39</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Ateles ater</t>
-        </is>
+    <row r="39" spans="1:3">
+      <c r="B39" t="s">
+        <v>40</v>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Cebus apella</t>
-        </is>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>42</v>
       </c>
       <c r="C40">
         <v>5</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Chlorocebus sabaeus</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Cercopithecus pygerythrus</t>
-        </is>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" t="s">
+        <v>44</v>
       </c>
       <c r="C41">
         <v>6</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Lagothrix lagotricha</t>
-        </is>
+    <row r="42" spans="1:3">
+      <c r="B42" t="s">
+        <v>45</v>
       </c>
       <c r="C42">
         <v>5</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Macaca irus</t>
-        </is>
+    <row r="43" spans="1:3">
+      <c r="B43" t="s">
+        <v>46</v>
       </c>
       <c r="C43">
         <v>6</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>47</v>
       </c>
       <c r="C44">
         <v>6</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Papio papio</t>
-        </is>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
       </c>
       <c r="C45">
         <v>6</v>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
+    <row r="46" spans="1:3">
+      <c r="B46" t="s">
+        <v>50</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Saimiri boliviensis boliviensis</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" t="s">
+        <v>52</v>
       </c>
       <c r="C47">
         <v>5</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Mus musculus</t>
-        </is>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>53</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Equus</t>
-        </is>
+    <row r="49" spans="1:3">
+      <c r="B49" t="s">
+        <v>54</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Didelphis virginiana</t>
-        </is>
+    <row r="50" spans="1:3">
+      <c r="B50" t="s">
+        <v>55</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Pongo pygmaeus</t>
-        </is>
+    <row r="51" spans="1:3">
+      <c r="B51" t="s">
+        <v>56</v>
       </c>
       <c r="C51">
         <v>6</v>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Manis pentadactyla</t>
-        </is>
+    <row r="52" spans="1:3">
+      <c r="B52" t="s">
+        <v>57</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Trichosurus vulpecula</t>
-        </is>
+    <row r="53" spans="1:3">
+      <c r="B53" t="s">
+        <v>58</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Microsorex hoyi</t>
-        </is>
+    <row r="54" spans="1:3">
+      <c r="B54" t="s">
+        <v>59</v>
       </c>
       <c r="C54">
         <v>2</v>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Setonix brachyurus</t>
-        </is>
+    <row r="55" spans="1:3">
+      <c r="B55" t="s">
+        <v>60</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Oryctolagus cuniculus</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Oryctolagus cuniculus</t>
-        </is>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" t="s">
+        <v>61</v>
       </c>
       <c r="C56">
         <v>2</v>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Procyon lotor</t>
-        </is>
+    <row r="57" spans="1:3">
+      <c r="B57" t="s">
+        <v>62</v>
       </c>
       <c r="C57">
         <v>3</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Rattus norvegicus</t>
-        </is>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" t="s">
+        <v>63</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Procavia capensis</t>
-        </is>
+    <row r="59" spans="1:3">
+      <c r="B59" t="s">
+        <v>64</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Callorhinus ursinus</t>
-        </is>
+    <row r="60" spans="1:3">
+      <c r="B60" t="s">
+        <v>65</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Ovis aries</t>
-        </is>
+    <row r="61" spans="1:3">
+      <c r="B61" t="s">
+        <v>66</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Nycticebus coucang</t>
-        </is>
+    <row r="62" spans="1:3">
+      <c r="B62" t="s">
+        <v>67</v>
       </c>
       <c r="C62">
         <v>5</v>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Tachyglossus aculeatus</t>
-        </is>
+    <row r="63" spans="1:3">
+      <c r="B63" t="s">
+        <v>68</v>
       </c>
       <c r="C63">
         <v>2</v>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Sciurus hudsonius</t>
-        </is>
+    <row r="64" spans="1:3">
+      <c r="B64" t="s">
+        <v>69</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Tapirus</t>
-        </is>
+    <row r="65" spans="1:3">
+      <c r="B65" t="s">
+        <v>70</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Tarsius</t>
-        </is>
+    <row r="66" spans="1:3">
+      <c r="B66" t="s">
+        <v>71</v>
       </c>
       <c r="C66">
         <v>4</v>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Potorous apicalis</t>
-        </is>
+    <row r="67" spans="1:3">
+      <c r="B67" t="s">
+        <v>72</v>
       </c>
       <c r="C67">
         <v>2</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Tupaia belangeri</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Tupaia glis</t>
-        </is>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Phocoena phocoena</t>
-        </is>
+    <row r="69" spans="1:3">
+      <c r="B69" t="s">
+        <v>75</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Marmota monax</t>
-        </is>
+    <row r="70" spans="1:3">
+      <c r="B70" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1404,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2E7700D-83C7-4BDE-8B85-96E8CCCFF322}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29ABB94-A221-4FBF-AF16-FC0A2BBBDDDC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A410ACC8-8DBF-4011-946B-C6FCA3B1DD23}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33D987E-62D3-4D6A-96F4-8CB88D0782A1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EA7B8FF-ECD6-4053-8593-786B7C46701D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25155E8A-625A-4D25-B352-13F99AAB8596}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A29ABB94-A221-4FBF-AF16-FC0A2BBBDDDC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{118B04A8-3CD3-4434-B06B-52D95741DE41}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33D987E-62D3-4D6A-96F4-8CB88D0782A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DE15439-602A-456C-B4D6-69CEB03F1DB3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25155E8A-625A-4D25-B352-13F99AAB8596}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9DDD189-43DB-4B40-8AB4-E5F8E3843C53}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{118B04A8-3CD3-4434-B06B-52D95741DE41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EB43874-4DF0-41E9-8AB9-14F1FA57C59B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DE15439-602A-456C-B4D6-69CEB03F1DB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8309EE1B-EA97-427E-8630-903D4C4F8FC4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9DDD189-43DB-4B40-8AB4-E5F8E3843C53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69D90BE6-5A11-4D00-81A2-A6FB5A55B95E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1192,291 +1192,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EB43874-4DF0-41E9-8AB9-14F1FA57C59B}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8309EE1B-EA97-427E-8630-903D4C4F8FC4}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69D90BE6-5A11-4D00-81A2-A6FB5A55B95E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1192,4 +1192,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{780FE2BB-AB3C-434C-B04E-1432CAC5EF5F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{214E5BE9-341C-4475-8F10-6ECFF92F8761}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF72D627-A6A0-4D16-8EB3-561784BD9EC3}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1192,291 +1192,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{780FE2BB-AB3C-434C-B04E-1432CAC5EF5F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{214E5BE9-341C-4475-8F10-6ECFF92F8761}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF72D627-A6A0-4D16-8EB3-561784BD9EC3}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1192,4 +1192,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CB40942-542E-44E8-A13B-F2164F833EF4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{123CD37B-5ED8-4103-B4C5-95CD9B1EC3E1}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6A7BDF0-E012-44FE-B7E4-86A4346377ED}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CB40942-542E-44E8-A13B-F2164F833EF4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{426C81F3-C46C-4236-81F7-DE0DFB7FAC67}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{123CD37B-5ED8-4103-B4C5-95CD9B1EC3E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A44CEE2-B597-43B2-810D-F4F5DA91A003}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6A7BDF0-E012-44FE-B7E4-86A4346377ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B776B93-0611-42BF-AC6E-250E09658702}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{426C81F3-C46C-4236-81F7-DE0DFB7FAC67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{658C2AAC-23BC-418A-ADCF-6A465EA47908}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A44CEE2-B597-43B2-810D-F4F5DA91A003}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{374BCA7F-1272-408C-9AB0-46599C77882B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B776B93-0611-42BF-AC6E-250E09658702}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E8375A7-FEE8-4D22-A28C-4DA43247A76F}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{658C2AAC-23BC-418A-ADCF-6A465EA47908}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69621E91-EEC7-4EFE-825D-5A0DE031B509}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{374BCA7F-1272-408C-9AB0-46599C77882B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EE72589-B010-436A-B9B1-4B8BDB2DF8CA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E8375A7-FEE8-4D22-A28C-4DA43247A76F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08D600A0-F8B3-492D-9DBA-9E0AD4BBEAFD}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69621E91-EEC7-4EFE-825D-5A0DE031B509}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5457B18C-AB29-4C5F-9171-423EDA7E8B7A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EE72589-B010-436A-B9B1-4B8BDB2DF8CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{205FC0CC-B8DB-4E51-99C5-EEBB4F8A1F93}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08D600A0-F8B3-492D-9DBA-9E0AD4BBEAFD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7B63E7B-E256-4281-A594-67CA2FDCD97B}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5457B18C-AB29-4C5F-9171-423EDA7E8B7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D405DB3-2CFD-435B-8FA7-A3A390E3BAD0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{205FC0CC-B8DB-4E51-99C5-EEBB4F8A1F93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB70642C-68D5-49BC-995C-FB849E68A524}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7B63E7B-E256-4281-A594-67CA2FDCD97B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A958B7DB-D6E7-4579-91C4-C80286BD22F9}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1192,291 +1192,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D405DB3-2CFD-435B-8FA7-A3A390E3BAD0}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB70642C-68D5-49BC-995C-FB849E68A524}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A958B7DB-D6E7-4579-91C4-C80286BD22F9}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1192,4 +1192,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B49A0F3-C66D-4F1D-ACD1-66CBB794AC35}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2D177A6-1469-48BD-BD84-6F5F5030675D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E46D366E-44AF-4838-9DF6-E4086160CB2F}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B49A0F3-C66D-4F1D-ACD1-66CBB794AC35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDF52EEE-DDF7-46D2-A498-87E6979F1ABA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2D177A6-1469-48BD-BD84-6F5F5030675D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2DB21E9-5DA0-412C-927F-9B849E932B8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E46D366E-44AF-4838-9DF6-E4086160CB2F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{089FEC64-DDB7-4442-A490-802B342085FC}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDF52EEE-DDF7-46D2-A498-87E6979F1ABA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{464367F1-D545-4D96-8ECD-985CDBD7C93C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2DB21E9-5DA0-412C-927F-9B849E932B8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C20F9938-E196-4D18-BC07-53CE88969993}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{089FEC64-DDB7-4442-A490-802B342085FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C447484-9D3A-4362-A811-6D797F971F8B}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{464367F1-D545-4D96-8ECD-985CDBD7C93C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5334435-C1D8-4DC2-A053-6E62684BF09B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C20F9938-E196-4D18-BC07-53CE88969993}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D4232A4-CD7B-4ADA-B78D-7B94D8B761AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C447484-9D3A-4362-A811-6D797F971F8B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E644A08-B553-4644-986B-2AC08A87D697}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5334435-C1D8-4DC2-A053-6E62684BF09B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5C5B76B-3631-4DAB-B602-9CF766547E80}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D4232A4-CD7B-4ADA-B78D-7B94D8B761AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5AA876F-D265-4CC2-9268-2EBD081A96C4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E644A08-B553-4644-986B-2AC08A87D697}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61FB7220-C386-4873-9A87-4339AC295A62}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1470,13 +1470,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5C5B76B-3631-4DAB-B602-9CF766547E80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C896D3FC-1FF7-49FC-9589-8A101B60FED6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5AA876F-D265-4CC2-9268-2EBD081A96C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE76A40D-AC56-4106-B204-E20BA237C9E2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61FB7220-C386-4873-9A87-4339AC295A62}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B674F98-33B3-42FA-909A-859E86FDAA4A}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1192,291 +1192,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C896D3FC-1FF7-49FC-9589-8A101B60FED6}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE76A40D-AC56-4106-B204-E20BA237C9E2}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B674F98-33B3-42FA-909A-859E86FDAA4A}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1192,4 +1192,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{832BC429-95D7-46C2-89EC-F0675E6E3254}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{515618FB-3E38-45DB-96BF-CAD2402226B2}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECC3A576-A797-4B6F-9E65-DA2467A1E13F}"/>
 </file>